--- a/statistics_files/2026/2026_99_e_borrower_count_zipcode.xlsx
+++ b/statistics_files/2026/2026_99_e_borrower_count_zipcode.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{363C284C-9044-4721-8B38-E850443F2539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42048019-0CD4-4C43-A927-3C6CC108A4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="January" sheetId="1" r:id="rId1"/>
@@ -235,7 +235,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1078,7 +1078,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:F2195"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -27872,14 +27872,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F2195"/>
+  <autoFilter ref="A1:F2195" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -27911,14 +27911,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -27950,14 +27950,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-00000A000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -27989,14 +27989,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-00000B000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -28028,14 +28028,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -28067,14 +28067,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -28106,14 +28106,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -28145,14 +28145,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -28184,14 +28184,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -28223,14 +28223,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -28262,14 +28262,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -28301,7 +28301,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
